--- a/Chapter.12/Practice_Java.xlsx
+++ b/Chapter.12/Practice_Java.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\Practice_Java\Chapter.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CDEF18-7774-40C6-84AC-FB53B49C7FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990403DC-FBF2-4FCF-A6B1-4A4BA4FD4DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="975" windowWidth="15855" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
   <si>
     <t>第12章　総仕上げ問題①</t>
     <rPh sb="0" eb="1">
@@ -223,13 +223,55 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>defと20の間の空白は何？</t>
+    <rPh sb="7" eb="8">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>クウハク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>build指定はjavacかな。JavacはA,B,C,DもOK。</t>
+    <rPh sb="5" eb="7">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C-X,D-X</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A,B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A,E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>testメソッドの引数が異なる。</t>
+    <rPh sb="9" eb="11">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -553,7 +595,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -580,28 +622,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -613,6 +641,13 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -949,7 +984,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="22" t="str">
-        <f>IF(C5="","",IF(C5=D5,"〇","✕"))</f>
+        <f t="shared" ref="E5:E14" si="0">IF(C5="","",(IF(D5="","",IF(C5=D5,"〇","✕"))))</f>
         <v>〇</v>
       </c>
       <c r="F5" s="18"/>
@@ -965,7 +1000,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="23" t="str">
-        <f>IF(C6="","",IF(C6=D6,"〇","✕"))</f>
+        <f t="shared" si="0"/>
         <v>〇</v>
       </c>
       <c r="F6" s="19"/>
@@ -981,7 +1016,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="24" t="str">
-        <f t="shared" ref="E7:E70" si="0">IF(C7="","",IF(C7=D7,"〇","✕"))</f>
+        <f t="shared" si="0"/>
         <v>✕</v>
       </c>
       <c r="F7" s="19" t="s">
@@ -1112,11 +1147,15 @@
       <c r="B15" s="3">
         <v>11</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="2"/>
+      <c r="C15" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E15" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(C15="","",(IF(D15="","",IF(C15=D15,"〇","✕"))))</f>
+        <v>〇</v>
       </c>
       <c r="F15" s="19"/>
     </row>
@@ -1124,11 +1163,15 @@
       <c r="B16" s="3">
         <v>12</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="2"/>
+      <c r="C16" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E16" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" ref="E16:E79" si="1">IF(C16="","",(IF(D16="","",IF(C16=D16,"〇","✕"))))</f>
+        <v>〇</v>
       </c>
       <c r="F16" s="19"/>
     </row>
@@ -1136,23 +1179,33 @@
       <c r="B17" s="3">
         <v>13</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F17" s="19"/>
+      <c r="C17" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="3">
         <v>14</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="2"/>
+      <c r="C18" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E18" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>〇</v>
       </c>
       <c r="F18" s="19"/>
     </row>
@@ -1160,23 +1213,33 @@
       <c r="B19" s="3">
         <v>15</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F19" s="19"/>
+      <c r="C19" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="3">
         <v>16</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="2"/>
+      <c r="C20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E20" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>〇</v>
       </c>
       <c r="F20" s="19"/>
     </row>
@@ -1184,23 +1247,33 @@
       <c r="B21" s="3">
         <v>17</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F21" s="19"/>
+      <c r="C21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="3">
         <v>18</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="2"/>
+      <c r="C22" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E22" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>〇</v>
       </c>
       <c r="F22" s="19"/>
     </row>
@@ -1208,11 +1281,15 @@
       <c r="B23" s="3">
         <v>19</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="2"/>
+      <c r="C23" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E23" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>〇</v>
       </c>
       <c r="F23" s="19"/>
     </row>
@@ -1220,13 +1297,19 @@
       <c r="B24" s="3">
         <v>20</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="2"/>
+      <c r="C24" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E24" s="23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F24" s="19"/>
+        <f t="shared" si="1"/>
+        <v>〇</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="3">
@@ -1235,7 +1318,7 @@
       <c r="C25" s="12"/>
       <c r="D25" s="2"/>
       <c r="E25" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F25" s="19"/>
@@ -1247,7 +1330,7 @@
       <c r="C26" s="12"/>
       <c r="D26" s="2"/>
       <c r="E26" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F26" s="19"/>
@@ -1259,7 +1342,7 @@
       <c r="C27" s="12"/>
       <c r="D27" s="2"/>
       <c r="E27" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F27" s="19"/>
@@ -1271,7 +1354,7 @@
       <c r="C28" s="12"/>
       <c r="D28" s="2"/>
       <c r="E28" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F28" s="19"/>
@@ -1283,7 +1366,7 @@
       <c r="C29" s="12"/>
       <c r="D29" s="2"/>
       <c r="E29" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F29" s="19"/>
@@ -1295,7 +1378,7 @@
       <c r="C30" s="12"/>
       <c r="D30" s="2"/>
       <c r="E30" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F30" s="19"/>
@@ -1307,7 +1390,7 @@
       <c r="C31" s="12"/>
       <c r="D31" s="2"/>
       <c r="E31" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F31" s="19"/>
@@ -1319,7 +1402,7 @@
       <c r="C32" s="12"/>
       <c r="D32" s="2"/>
       <c r="E32" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F32" s="19"/>
@@ -1331,7 +1414,7 @@
       <c r="C33" s="12"/>
       <c r="D33" s="2"/>
       <c r="E33" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F33" s="19"/>
@@ -1343,7 +1426,7 @@
       <c r="C34" s="12"/>
       <c r="D34" s="2"/>
       <c r="E34" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F34" s="19"/>
@@ -1355,7 +1438,7 @@
       <c r="C35" s="12"/>
       <c r="D35" s="2"/>
       <c r="E35" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F35" s="19"/>
@@ -1367,7 +1450,7 @@
       <c r="C36" s="12"/>
       <c r="D36" s="2"/>
       <c r="E36" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F36" s="19"/>
@@ -1379,7 +1462,7 @@
       <c r="C37" s="12"/>
       <c r="D37" s="2"/>
       <c r="E37" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F37" s="19"/>
@@ -1391,7 +1474,7 @@
       <c r="C38" s="12"/>
       <c r="D38" s="2"/>
       <c r="E38" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F38" s="19"/>
@@ -1403,7 +1486,7 @@
       <c r="C39" s="12"/>
       <c r="D39" s="2"/>
       <c r="E39" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F39" s="19"/>
@@ -1415,7 +1498,7 @@
       <c r="C40" s="12"/>
       <c r="D40" s="2"/>
       <c r="E40" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F40" s="19"/>
@@ -1427,7 +1510,7 @@
       <c r="C41" s="12"/>
       <c r="D41" s="2"/>
       <c r="E41" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F41" s="19"/>
@@ -1439,7 +1522,7 @@
       <c r="C42" s="12"/>
       <c r="D42" s="2"/>
       <c r="E42" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F42" s="19"/>
@@ -1451,7 +1534,7 @@
       <c r="C43" s="12"/>
       <c r="D43" s="2"/>
       <c r="E43" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F43" s="19"/>
@@ -1463,7 +1546,7 @@
       <c r="C44" s="12"/>
       <c r="D44" s="2"/>
       <c r="E44" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F44" s="19"/>
@@ -1475,7 +1558,7 @@
       <c r="C45" s="12"/>
       <c r="D45" s="2"/>
       <c r="E45" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F45" s="19"/>
@@ -1487,7 +1570,7 @@
       <c r="C46" s="12"/>
       <c r="D46" s="2"/>
       <c r="E46" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F46" s="19"/>
@@ -1499,7 +1582,7 @@
       <c r="C47" s="12"/>
       <c r="D47" s="2"/>
       <c r="E47" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F47" s="19"/>
@@ -1511,7 +1594,7 @@
       <c r="C48" s="12"/>
       <c r="D48" s="2"/>
       <c r="E48" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F48" s="19"/>
@@ -1523,7 +1606,7 @@
       <c r="C49" s="12"/>
       <c r="D49" s="2"/>
       <c r="E49" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F49" s="19"/>
@@ -1535,7 +1618,7 @@
       <c r="C50" s="12"/>
       <c r="D50" s="2"/>
       <c r="E50" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F50" s="19"/>
@@ -1547,7 +1630,7 @@
       <c r="C51" s="12"/>
       <c r="D51" s="2"/>
       <c r="E51" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F51" s="19"/>
@@ -1559,7 +1642,7 @@
       <c r="C52" s="12"/>
       <c r="D52" s="2"/>
       <c r="E52" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F52" s="19"/>
@@ -1571,7 +1654,7 @@
       <c r="C53" s="12"/>
       <c r="D53" s="2"/>
       <c r="E53" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F53" s="19"/>
@@ -1583,7 +1666,7 @@
       <c r="C54" s="12"/>
       <c r="D54" s="2"/>
       <c r="E54" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F54" s="19"/>
@@ -1595,7 +1678,7 @@
       <c r="C55" s="12"/>
       <c r="D55" s="2"/>
       <c r="E55" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F55" s="19"/>
@@ -1607,7 +1690,7 @@
       <c r="C56" s="12"/>
       <c r="D56" s="2"/>
       <c r="E56" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F56" s="19"/>
@@ -1619,7 +1702,7 @@
       <c r="C57" s="12"/>
       <c r="D57" s="2"/>
       <c r="E57" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F57" s="19"/>
@@ -1631,7 +1714,7 @@
       <c r="C58" s="12"/>
       <c r="D58" s="2"/>
       <c r="E58" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F58" s="19"/>
@@ -1643,7 +1726,7 @@
       <c r="C59" s="12"/>
       <c r="D59" s="2"/>
       <c r="E59" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F59" s="19"/>
@@ -1655,7 +1738,7 @@
       <c r="C60" s="12"/>
       <c r="D60" s="2"/>
       <c r="E60" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F60" s="19"/>
@@ -1667,7 +1750,7 @@
       <c r="C61" s="12"/>
       <c r="D61" s="2"/>
       <c r="E61" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F61" s="19"/>
@@ -1679,7 +1762,7 @@
       <c r="C62" s="12"/>
       <c r="D62" s="2"/>
       <c r="E62" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F62" s="19"/>
@@ -1691,7 +1774,7 @@
       <c r="C63" s="12"/>
       <c r="D63" s="2"/>
       <c r="E63" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F63" s="19"/>
@@ -1703,7 +1786,7 @@
       <c r="C64" s="12"/>
       <c r="D64" s="2"/>
       <c r="E64" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F64" s="19"/>
@@ -1715,7 +1798,7 @@
       <c r="C65" s="12"/>
       <c r="D65" s="2"/>
       <c r="E65" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F65" s="19"/>
@@ -1727,7 +1810,7 @@
       <c r="C66" s="12"/>
       <c r="D66" s="2"/>
       <c r="E66" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F66" s="19"/>
@@ -1739,7 +1822,7 @@
       <c r="C67" s="12"/>
       <c r="D67" s="2"/>
       <c r="E67" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F67" s="19"/>
@@ -1751,7 +1834,7 @@
       <c r="C68" s="12"/>
       <c r="D68" s="2"/>
       <c r="E68" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F68" s="19"/>
@@ -1763,7 +1846,7 @@
       <c r="C69" s="12"/>
       <c r="D69" s="2"/>
       <c r="E69" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F69" s="19"/>
@@ -1775,7 +1858,7 @@
       <c r="C70" s="12"/>
       <c r="D70" s="2"/>
       <c r="E70" s="23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F70" s="19"/>
@@ -1787,7 +1870,7 @@
       <c r="C71" s="12"/>
       <c r="D71" s="2"/>
       <c r="E71" s="23" t="str">
-        <f t="shared" ref="E71:E84" si="1">IF(C71="","",IF(C71=D71,"〇","✕"))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F71" s="19"/>
@@ -1895,7 +1978,7 @@
       <c r="C80" s="12"/>
       <c r="D80" s="2"/>
       <c r="E80" s="23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E80:E84" si="2">IF(C80="","",(IF(D80="","",IF(C80=D80,"〇","✕"))))</f>
         <v/>
       </c>
       <c r="F80" s="19"/>
@@ -1907,7 +1990,7 @@
       <c r="C81" s="12"/>
       <c r="D81" s="2"/>
       <c r="E81" s="23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="F81" s="19"/>
@@ -1919,7 +2002,7 @@
       <c r="C82" s="12"/>
       <c r="D82" s="2"/>
       <c r="E82" s="23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="F82" s="19"/>
@@ -1931,7 +2014,7 @@
       <c r="C83" s="12"/>
       <c r="D83" s="2"/>
       <c r="E83" s="23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="F83" s="19"/>
@@ -1943,7 +2026,7 @@
       <c r="C84" s="13"/>
       <c r="D84" s="9"/>
       <c r="E84" s="25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="F84" s="20"/>
@@ -1951,15 +2034,15 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThanOrEqual">
-      <formula>0.7</formula>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
+      <formula>0.629</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>0.699</formula>
       <formula>0.633</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThanOrEqual">
-      <formula>0.629</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
+      <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Chapter.12/Practice_Java.xlsx
+++ b/Chapter.12/Practice_Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\Practice_Java\Chapter.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990403DC-FBF2-4FCF-A6B1-4A4BA4FD4DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FBD968-8D32-4E3E-B753-53B38B9E9F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="975" windowWidth="15855" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="150" yWindow="900" windowWidth="15855" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="37">
   <si>
     <t>第12章　総仕上げ問題①</t>
     <rPh sb="0" eb="1">
@@ -150,28 +150,6 @@
       <t>ブン</t>
     </rPh>
     <rPh sb="18" eb="20">
-      <t>ミオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aはjmod作るとき。Cは実行時。Dはjarファイル作るとき。→問題文見落とし</t>
-    <rPh sb="6" eb="7">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ジッコウジ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
       <t>ミオ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -237,17 +215,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>build指定はjavacかな。JavacはA,B,C,DもOK。</t>
-    <rPh sb="5" eb="7">
-      <t>シテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>C-X,D-X</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>A,B</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -263,6 +230,277 @@
     <rPh sb="12" eb="13">
       <t>コト</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// A. ローカル変数は、finalを付けて宣言できる。
+// → 〇 ： 変更（再代入）はできない。
+// B. インタフェースは、protectedを付けて宣言できる。
+// → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ： できません。only public, private, abstract, default, static and strictfpと
+// エラーメッセージが言ってます。
+// C. インスタンス変数はstaticを付けて宣言できる。
+// → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ： できません。static付けた時点でインスタンス変数ではなくなります。
+// D. 抽象メソッドは、privateを付けて宣言できる。
+// → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ： できません。それだと実装できなくなります。
+// E. インナークラスは、publicを付けて宣言できる。
+// → 〇 ： できます。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>build指定はjavacかな。JavacはA,B,C,DもOK。
+Aは、javac ex15/Sample.java ex15/Main.javaで同じdirにclassは作るが、java -cp build ex15.Mainでbuildを指定されてもNG。Bは、javac -d build ex15/Sample.java ex15/Main.javaでbuild配下に作成。java -cp build ex15.Mainで動く。Cは、java ex15.Main でbuild配下でないのでNG。Dは、java build.ex15.Main でNG。</t>
+    <rPh sb="5" eb="7">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="186" eb="188">
+      <t>ハイカ</t>
+    </rPh>
+    <rPh sb="189" eb="191">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="217" eb="218">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="244" eb="246">
+      <t>ハイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aはjmod作るとき。Cは実行時。Dはjarファイル作るとき。→問題文見落とし
+&gt;jdeps AppService.class
+AppService.class -&gt; java.base
+AppService.class -&gt; 見つかりません
+   app　-&gt; function　見つかりません
+   app　-&gt; java.io　 java.base
+   app　-&gt; java.lang                                          java.base</t>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ジッコウジ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ミオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>配列の切り方と設定の仕方</t>
+    <rPh sb="0" eb="2">
+      <t>ハイレツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シカタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A,B,E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A,C,E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a2.sample(list);を実行すると、Bが表示される。インスタンスをA型として扱っていたとしてもBクラスでオーバーライドしたメソッドが実行される。また、引数に互換性がある場合、より厳密なほうを選択する。</t>
+    <rPh sb="39" eb="40">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>アツカ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="83" eb="86">
+      <t>ゴカンセイ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ゲンミツ</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>菱形継承問題。B,Cどちらか判定できず。</t>
+    <rPh sb="0" eb="6">
+      <t>ヒシガタケイショウモンダイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実装じゃなく、オーバーロードですよ。それ。</t>
+    <rPh sb="0" eb="2">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A: O  B:O C:O D:x E:O。Dのみ上位→下位。</t>
+    <rPh sb="25" eb="27">
+      <t>ジョウイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A,E,F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インタフェース（公開する扱い方、インスタンス化できず、抽象メソッド）
+A:　Aはfinalにできない。→　正しい（具象化するので・・・）
+B:　Bはabstractにできない。→　正しい（インスタンス生成してる→抽象不可）
+C:　Bはfinalにできない。→　誤り（できる）。
+D:    AはBのサブタイプである。　→　誤り
+E:    Aはabstractにできない。　→　誤り（できる）。
+F:    BはAのサブタイプである。　→　正しい。</t>
+    <rPh sb="8" eb="10">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アツカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>チュウショウ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="58" eb="61">
+      <t>グショウカ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="162" eb="163">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="190" eb="191">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="221" eb="222">
+      <t>タダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A,B,F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JREのモジュール jlink
+jlinkでカスタムJREを作成しコンテナ・サイズを削減</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -946,7 +1184,7 @@
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="26">
         <f>COUNTIF(E5:E84,"〇")/(COUNTIF(E5:E84,"〇")+COUNTIF(E5:E84,"✕"))</f>
@@ -967,7 +1205,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>4</v>
@@ -1020,7 +1258,7 @@
         <v>✕</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="2:6">
@@ -1107,7 +1345,7 @@
       </c>
       <c r="F12" s="19"/>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:6" ht="131.25">
       <c r="B13" s="3">
         <v>9</v>
       </c>
@@ -1122,7 +1360,7 @@
         <v>✕</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:6">
@@ -1190,7 +1428,7 @@
         <v>✕</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -1209,7 +1447,7 @@
       </c>
       <c r="F18" s="19"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" ht="93.75">
       <c r="B19" s="3">
         <v>15</v>
       </c>
@@ -1224,7 +1462,7 @@
         <v>✕</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="2:6">
@@ -1243,22 +1481,22 @@
       </c>
       <c r="F20" s="19"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" ht="206.25">
       <c r="B21" s="3">
         <v>17</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F21" s="19" t="s">
         <v>23</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>✕</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -1308,126 +1546,180 @@
         <v>〇</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="3">
         <v>21</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="19"/>
+      <c r="C25" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="3">
         <v>22</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="2"/>
+      <c r="C26" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E26" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F26" s="19"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" ht="56.25">
       <c r="B27" s="3">
         <v>23</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F27" s="19"/>
+      <c r="C27" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="3">
         <v>24</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="2"/>
+      <c r="C28" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E28" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="3">
         <v>25</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="2"/>
+      <c r="C29" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E29" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="3">
         <v>26</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="2"/>
+      <c r="C30" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E30" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="3">
         <v>27</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="2"/>
+      <c r="C31" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E31" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F31" s="19"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="150">
       <c r="B32" s="3">
         <v>28</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="19"/>
-    </row>
-    <row r="33" spans="2:6">
+      <c r="C32" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="37.5">
       <c r="B33" s="3">
         <v>29</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="2"/>
+      <c r="C33" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E33" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="3">
         <v>30</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="2"/>
+      <c r="C34" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E34" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F34" s="19"/>
     </row>

--- a/Chapter.12/Practice_Java.xlsx
+++ b/Chapter.12/Practice_Java.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\Practice_Java\Chapter.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FBD968-8D32-4E3E-B753-53B38B9E9F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74916A6-3142-4662-A087-4A833C6EADFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="150" yWindow="900" windowWidth="15855" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="41">
   <si>
     <t>第12章　総仕上げ問題①</t>
     <rPh sb="0" eb="1">
@@ -503,6 +503,27 @@
 jlinkでカスタムJREを作成しコンテナ・サイズを削減</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>// 32. 抽象クラスの定義として、正しいものを選びなさい（１つ選択）。
+// B.メソッドにabstractがない。
+// C.メソッドにabstractがない。
+// finalは問題なし（printは抽象メソッドではない）。
+// D.abstractで処理かいちゃあかん。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UnsupportedOperationException
+List.ofはイミュータブル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>privateなのでオーバーライドされていない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C,E</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -533,7 +554,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -552,6 +573,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -789,7 +816,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -861,6 +888,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1188,7 +1221,7 @@
       </c>
       <c r="E3" s="26">
         <f>COUNTIF(E5:E84,"〇")/(COUNTIF(E5:E84,"〇")+COUNTIF(E5:E84,"✕"))</f>
-        <v>0.7</v>
+        <v>0.72972972972972971</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>5</v>
@@ -1727,47 +1760,67 @@
       <c r="B35" s="3">
         <v>31</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="2"/>
+      <c r="C35" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E35" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F35" s="19"/>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:6" ht="93.75">
       <c r="B36" s="3">
         <v>32</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="2"/>
+      <c r="C36" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E36" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F36" s="19"/>
-    </row>
-    <row r="37" spans="2:6">
+        <v>〇</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" ht="37.5">
       <c r="B37" s="3">
         <v>33</v>
       </c>
-      <c r="C37" s="12"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F37" s="19"/>
+      <c r="C37" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="3">
         <v>34</v>
       </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="2"/>
+      <c r="C38" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E38" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F38" s="19"/>
     </row>
@@ -1775,23 +1828,33 @@
       <c r="B39" s="3">
         <v>35</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="2"/>
+      <c r="C39" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E39" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F39" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="3">
         <v>36</v>
       </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="2"/>
+      <c r="C40" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E40" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F40" s="19"/>
     </row>
@@ -1799,11 +1862,15 @@
       <c r="B41" s="3">
         <v>37</v>
       </c>
-      <c r="C41" s="12"/>
-      <c r="D41" s="2"/>
+      <c r="C41" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E41" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F41" s="19"/>
     </row>
@@ -1811,7 +1878,9 @@
       <c r="B42" s="3">
         <v>38</v>
       </c>
-      <c r="C42" s="12"/>
+      <c r="C42" s="12" t="s">
+        <v>6</v>
+      </c>
       <c r="D42" s="2"/>
       <c r="E42" s="23" t="str">
         <f t="shared" si="1"/>
@@ -1823,7 +1892,9 @@
       <c r="B43" s="3">
         <v>39</v>
       </c>
-      <c r="C43" s="12"/>
+      <c r="C43" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="D43" s="2"/>
       <c r="E43" s="23" t="str">
         <f t="shared" si="1"/>

--- a/Chapter.12/Practice_Java.xlsx
+++ b/Chapter.12/Practice_Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\Practice_Java\Chapter.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74916A6-3142-4662-A087-4A833C6EADFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55025D9-EAE3-4298-8707-CB4467A6AE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="900" windowWidth="15855" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2715" yWindow="915" windowWidth="15855" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="41">
   <si>
     <t>第12章　総仕上げ問題①</t>
     <rPh sb="0" eb="1">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E3" s="26">
         <f>COUNTIF(E5:E84,"〇")/(COUNTIF(E5:E84,"〇")+COUNTIF(E5:E84,"✕"))</f>
-        <v>0.72972972972972971</v>
+        <v>0.75609756097560976</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>5</v>
@@ -1881,10 +1881,12 @@
       <c r="C42" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="2"/>
+      <c r="D42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E42" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F42" s="19"/>
     </row>
@@ -1895,10 +1897,12 @@
       <c r="C43" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E43" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F43" s="19"/>
     </row>
@@ -1906,11 +1910,15 @@
       <c r="B44" s="3">
         <v>40</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="2"/>
+      <c r="C44" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E44" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F44" s="19"/>
     </row>
@@ -1918,11 +1926,15 @@
       <c r="B45" s="3">
         <v>41</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="2"/>
+      <c r="C45" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E45" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F45" s="19"/>
     </row>

--- a/Chapter.12/Practice_Java.xlsx
+++ b/Chapter.12/Practice_Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\Practice_Java\Chapter.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55025D9-EAE3-4298-8707-CB4467A6AE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804B5A8D-4F6F-461D-AEDB-69D8421A760D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="915" windowWidth="15855" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7695" yWindow="2700" windowWidth="21345" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="46">
   <si>
     <t>第12章　総仕上げ問題①</t>
     <rPh sb="0" eb="1">
@@ -522,6 +522,29 @@
   </si>
   <si>
     <t>C,E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>国際標準規格 (ISO 8601)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィールドはオーバライドされないため、A クラスのフィールドが参照されます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なんですかこれ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デフォルトコンストラクタ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>setA,setB,setCは動きません。</t>
+    <rPh sb="15" eb="16">
+      <t>ウゴ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1221,7 +1244,7 @@
       </c>
       <c r="E3" s="26">
         <f>COUNTIF(E5:E84,"〇")/(COUNTIF(E5:E84,"〇")+COUNTIF(E5:E84,"✕"))</f>
-        <v>0.75609756097560976</v>
+        <v>0.8</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>5</v>
@@ -1942,47 +1965,69 @@
       <c r="B46" s="3">
         <v>42</v>
       </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="2"/>
+      <c r="C46" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E46" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F46" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="3">
         <v>43</v>
       </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="2"/>
+      <c r="C47" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E47" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F47" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="3">
         <v>44</v>
       </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="2"/>
+      <c r="C48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E48" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F48" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="3">
         <v>45</v>
       </c>
-      <c r="C49" s="12"/>
-      <c r="D49" s="2"/>
+      <c r="C49" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E49" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F49" s="19"/>
     </row>
@@ -1990,23 +2035,33 @@
       <c r="B50" s="3">
         <v>46</v>
       </c>
-      <c r="C50" s="12"/>
-      <c r="D50" s="2"/>
+      <c r="C50" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E50" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F50" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="3">
         <v>47</v>
       </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="2"/>
+      <c r="C51" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E51" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F51" s="19"/>
     </row>
@@ -2014,23 +2069,33 @@
       <c r="B52" s="3">
         <v>48</v>
       </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="2"/>
+      <c r="C52" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E52" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F52" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="3">
         <v>49</v>
       </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="2"/>
+      <c r="C53" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E53" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F53" s="19"/>
     </row>
@@ -2038,11 +2103,15 @@
       <c r="B54" s="3">
         <v>50</v>
       </c>
-      <c r="C54" s="12"/>
-      <c r="D54" s="2"/>
+      <c r="C54" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E54" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F54" s="19"/>
     </row>

--- a/Chapter.12/Practice_Java.xlsx
+++ b/Chapter.12/Practice_Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\Practice_Java\Chapter.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804B5A8D-4F6F-461D-AEDB-69D8421A760D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7782242-9AA2-4D70-8926-1769FC4A1691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7695" yWindow="2700" windowWidth="21345" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-150" yWindow="1050" windowWidth="21345" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="48">
   <si>
     <t>第12章　総仕上げ問題①</t>
     <rPh sb="0" eb="1">
@@ -545,6 +545,14 @@
     <rPh sb="15" eb="16">
       <t>ウゴ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A,C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>try catch finally</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1244,7 +1252,7 @@
       </c>
       <c r="E3" s="26">
         <f>COUNTIF(E5:E84,"〇")/(COUNTIF(E5:E84,"〇")+COUNTIF(E5:E84,"✕"))</f>
-        <v>0.8</v>
+        <v>0.78846153846153844</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>5</v>
@@ -2119,23 +2127,33 @@
       <c r="B55" s="3">
         <v>51</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="2"/>
+      <c r="C55" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="E55" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F55" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="3">
         <v>52</v>
       </c>
-      <c r="C56" s="12"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="C56" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
       </c>
       <c r="F56" s="19"/>
     </row>

--- a/Chapter.12/Practice_Java.xlsx
+++ b/Chapter.12/Practice_Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\Practice_Java\Chapter.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7782242-9AA2-4D70-8926-1769FC4A1691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E0CC0E-F765-49B0-930F-6F7184DB2472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-150" yWindow="1050" windowWidth="21345" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4245" yWindow="270" windowWidth="21345" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="53">
   <si>
     <t>第12章　総仕上げ問題①</t>
     <rPh sb="0" eb="1">
@@ -553,6 +553,56 @@
   </si>
   <si>
     <t>try catch finally</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A,B,D,F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブクラスのcatchを先に書く</t>
+    <rPh sb="12" eb="13">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凡ミス</t>
+    <rPh sb="0" eb="1">
+      <t>ボン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最初のa+bは数値足して文字列、後ろのaはその前の文字列とくっつく。</t>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ウシ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>モジレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンスタントプール</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1252,7 +1302,7 @@
       </c>
       <c r="E3" s="26">
         <f>COUNTIF(E5:E84,"〇")/(COUNTIF(E5:E84,"〇")+COUNTIF(E5:E84,"✕"))</f>
-        <v>0.78846153846153844</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>5</v>
@@ -2161,11 +2211,15 @@
       <c r="B57" s="3">
         <v>53</v>
       </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="2"/>
+      <c r="C57" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E57" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F57" s="19"/>
     </row>
@@ -2173,11 +2227,15 @@
       <c r="B58" s="3">
         <v>54</v>
       </c>
-      <c r="C58" s="12"/>
-      <c r="D58" s="2"/>
+      <c r="C58" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E58" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F58" s="19"/>
     </row>
@@ -2185,11 +2243,15 @@
       <c r="B59" s="3">
         <v>55</v>
       </c>
-      <c r="C59" s="12"/>
-      <c r="D59" s="2"/>
+      <c r="C59" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="E59" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F59" s="19"/>
     </row>
@@ -2197,11 +2259,15 @@
       <c r="B60" s="3">
         <v>56</v>
       </c>
-      <c r="C60" s="12"/>
-      <c r="D60" s="2"/>
+      <c r="C60" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E60" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F60" s="19"/>
     </row>
@@ -2209,47 +2275,69 @@
       <c r="B61" s="3">
         <v>57</v>
       </c>
-      <c r="C61" s="12"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F61" s="19"/>
+      <c r="C61" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="3">
         <v>58</v>
       </c>
-      <c r="C62" s="12"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F62" s="19"/>
+      <c r="C62" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="3">
         <v>59</v>
       </c>
-      <c r="C63" s="12"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F63" s="19"/>
+      <c r="C63" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="3">
         <v>60</v>
       </c>
-      <c r="C64" s="12"/>
-      <c r="D64" s="2"/>
+      <c r="C64" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E64" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F64" s="19"/>
     </row>
@@ -2257,23 +2345,33 @@
       <c r="B65" s="3">
         <v>61</v>
       </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="2"/>
+      <c r="C65" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E65" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F65" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="3">
         <v>62</v>
       </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="2"/>
+      <c r="C66" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E66" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F66" s="19"/>
     </row>
@@ -2281,11 +2379,15 @@
       <c r="B67" s="3">
         <v>63</v>
       </c>
-      <c r="C67" s="12"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="C67" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>✕</v>
       </c>
       <c r="F67" s="19"/>
     </row>
@@ -2293,11 +2395,15 @@
       <c r="B68" s="3">
         <v>64</v>
       </c>
-      <c r="C68" s="12"/>
-      <c r="D68" s="2"/>
+      <c r="C68" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E68" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F68" s="19"/>
     </row>
@@ -2305,11 +2411,15 @@
       <c r="B69" s="3">
         <v>65</v>
       </c>
-      <c r="C69" s="12"/>
-      <c r="D69" s="2"/>
+      <c r="C69" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E69" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F69" s="19"/>
     </row>

--- a/Chapter.12/Practice_Java.xlsx
+++ b/Chapter.12/Practice_Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\Practice_Java\Chapter.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E0CC0E-F765-49B0-930F-6F7184DB2472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F6B1B7-60BD-4239-845D-9BA5E83AAD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="270" windowWidth="21345" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8265" yWindow="2310" windowWidth="21345" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="55">
   <si>
     <t>第12章　総仕上げ問題①</t>
     <rPh sb="0" eb="1">
@@ -603,6 +603,32 @@
   </si>
   <si>
     <t>コンスタントプール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例外、エラーが吐き出される。でもexceptionではなくerror</t>
+    <rPh sb="0" eb="2">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>可変型変数は配列に。</t>
+    <rPh sb="0" eb="3">
+      <t>カヘンガタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハイレツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1302,7 +1328,7 @@
       </c>
       <c r="E3" s="26">
         <f>COUNTIF(E5:E84,"〇")/(COUNTIF(E5:E84,"〇")+COUNTIF(E5:E84,"✕"))</f>
-        <v>0.76923076923076927</v>
+        <v>0.77142857142857146</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>5</v>
@@ -2427,11 +2453,15 @@
       <c r="B70" s="3">
         <v>66</v>
       </c>
-      <c r="C70" s="12"/>
-      <c r="D70" s="2"/>
+      <c r="C70" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E70" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F70" s="19"/>
     </row>
@@ -2439,11 +2469,15 @@
       <c r="B71" s="3">
         <v>67</v>
       </c>
-      <c r="C71" s="12"/>
-      <c r="D71" s="2"/>
+      <c r="C71" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E71" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F71" s="19"/>
     </row>
@@ -2451,35 +2485,51 @@
       <c r="B72" s="3">
         <v>68</v>
       </c>
-      <c r="C72" s="12"/>
-      <c r="D72" s="2"/>
+      <c r="C72" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="E72" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F72" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="3">
         <v>69</v>
       </c>
-      <c r="C73" s="12"/>
-      <c r="D73" s="2"/>
+      <c r="C73" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E73" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F73" s="19"/>
+        <v>✕</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="3">
         <v>70</v>
       </c>
-      <c r="C74" s="12"/>
-      <c r="D74" s="2"/>
+      <c r="C74" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E74" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F74" s="19"/>
     </row>

--- a/Chapter.12/Practice_Java.xlsx
+++ b/Chapter.12/Practice_Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokan\study\Practice_Java\Chapter.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F6B1B7-60BD-4239-845D-9BA5E83AAD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0466F5B4-7210-482B-8AC2-706F955A09A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8265" yWindow="2310" windowWidth="21345" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="1860" windowWidth="21345" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="58">
   <si>
     <t>第12章　総仕上げ問題①</t>
     <rPh sb="0" eb="1">
@@ -629,6 +629,18 @@
     <rPh sb="6" eb="8">
       <t>ハイレツ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">The substring begins at the specified start and extends to the character at index end - 1 or to the end of the sequence if no such character exists. </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スーパークラスの型にサブクラスを代入したものであってもサブクラスのメソッド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>public protected</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1328,7 +1340,7 @@
       </c>
       <c r="E3" s="26">
         <f>COUNTIF(E5:E84,"〇")/(COUNTIF(E5:E84,"〇")+COUNTIF(E5:E84,"✕"))</f>
-        <v>0.77142857142857146</v>
+        <v>0.78749999999999998</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>5</v>
@@ -2506,10 +2518,10 @@
       <c r="C73" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E73" s="23" t="str">
+      <c r="D73" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E73" s="24" t="str">
         <f t="shared" si="1"/>
         <v>✕</v>
       </c>
@@ -2537,35 +2549,49 @@
       <c r="B75" s="3">
         <v>71</v>
       </c>
-      <c r="C75" s="12"/>
-      <c r="D75" s="2"/>
+      <c r="C75" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E75" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F75" s="19"/>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" ht="37.5">
       <c r="B76" s="3">
         <v>72</v>
       </c>
-      <c r="C76" s="12"/>
-      <c r="D76" s="2"/>
+      <c r="C76" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E76" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F76" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="3">
         <v>73</v>
       </c>
-      <c r="C77" s="12"/>
-      <c r="D77" s="2"/>
+      <c r="C77" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E77" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F77" s="19"/>
     </row>
@@ -2573,11 +2599,15 @@
       <c r="B78" s="3">
         <v>74</v>
       </c>
-      <c r="C78" s="12"/>
-      <c r="D78" s="2"/>
+      <c r="C78" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E78" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F78" s="19"/>
     </row>
@@ -2585,11 +2615,15 @@
       <c r="B79" s="3">
         <v>75</v>
       </c>
-      <c r="C79" s="12"/>
-      <c r="D79" s="2"/>
+      <c r="C79" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E79" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F79" s="19"/>
     </row>
@@ -2597,11 +2631,15 @@
       <c r="B80" s="3">
         <v>76</v>
       </c>
-      <c r="C80" s="12"/>
-      <c r="D80" s="2"/>
+      <c r="C80" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E80" s="23" t="str">
         <f t="shared" ref="E80:E84" si="2">IF(C80="","",(IF(D80="","",IF(C80=D80,"〇","✕"))))</f>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F80" s="19"/>
     </row>
@@ -2609,35 +2647,51 @@
       <c r="B81" s="3">
         <v>77</v>
       </c>
-      <c r="C81" s="12"/>
-      <c r="D81" s="2"/>
+      <c r="C81" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E81" s="23" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F81" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="3">
         <v>78</v>
       </c>
-      <c r="C82" s="12"/>
-      <c r="D82" s="2"/>
+      <c r="C82" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E82" s="23" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F82" s="19"/>
+        <v>〇</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="3">
         <v>79</v>
       </c>
-      <c r="C83" s="12"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="23" t="str">
+      <c r="C83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" s="24" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>✕</v>
       </c>
       <c r="F83" s="19"/>
     </row>
@@ -2645,11 +2699,15 @@
       <c r="B84" s="4">
         <v>80</v>
       </c>
-      <c r="C84" s="13"/>
-      <c r="D84" s="9"/>
+      <c r="C84" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="E84" s="25" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="F84" s="20"/>
     </row>
